--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484290_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484290_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0896</v>
+        <v>9.952199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1137</v>
+        <v>8.1942</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9759</v>
+        <v>1.758</v>
       </c>
       <c r="G2" t="n">
         <v>6.9617</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0693</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4153</v>
+        <v>-0.3349</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4846</v>
+        <v>0.2667</v>
       </c>
       <c r="V2" t="n">
         <v>1.4959</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1349</v>
+        <v>4.6543</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7268</v>
+        <v>3.1918</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4081</v>
+        <v>1.4626</v>
       </c>
       <c r="G3" t="n">
         <v>3.1027</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0555</v>
+        <v>0.575</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0384</v>
+        <v>0.4266</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0939</v>
+        <v>0.1484</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8449</v>
+        <v>2.4404</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3101</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="F4" t="n">
         <v>1.5348</v>
@@ -766,10 +766,10 @@
         <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4555</v>
+        <v>1.051</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0594</v>
+        <v>0.6549</v>
       </c>
       <c r="U4" t="n">
         <v>0.3961</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4543</v>
+        <v>2.264</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0176</v>
+        <v>1.3098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4367</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.4937</v>
@@ -844,13 +844,13 @@
         <v>2.3441</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0274</v>
+        <v>0.8371</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4914</v>
+        <v>0.7836</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4639</v>
+        <v>0.0535</v>
       </c>
       <c r="V5" t="n">
         <v>1.4959</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2704</v>
+        <v>1.3642</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3565</v>
+        <v>1.4775</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0861</v>
+        <v>-0.1134</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0022</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2548</v>
+        <v>-0.161</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0522</v>
+        <v>0.0689</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2027</v>
+        <v>-0.2299</v>
       </c>
       <c r="V6" t="n">
         <v>0.9414</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9946</v>
+        <v>1.0635</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5491</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3237</v>
+        <v>0.5144</v>
       </c>
       <c r="G7" t="n">
         <v>1.7361</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0269</v>
+        <v>0.0419</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1732</v>
+        <v>-0.295</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1463</v>
+        <v>0.3369</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4959</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1247</v>
+        <v>0.1792</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4397</v>
+        <v>0.6619</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5644</v>
+        <v>-0.4827</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0581</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2619</v>
+        <v>0.0419</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3692</v>
+        <v>-1.1863</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1908</v>
+        <v>-1.0897</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1783</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5212</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2619</v>
+        <v>-0.0791</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8832</v>
+        <v>-1.8961</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5187</v>
+        <v>-2.2862</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3645</v>
+        <v>0.39</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8084</v>
+        <v>-3.8217</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2663</v>
+        <v>-2.7025</v>
       </c>
       <c r="I10" t="n">
-        <v>0.458</v>
+        <v>-1.1192</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8629</v>
+        <v>-1.9786</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5912</v>
+        <v>-1.9392</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7284</v>
+        <v>-0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0545</v>
+        <v>-1.8431</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3249</v>
+        <v>-0.7634</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2704</v>
+        <v>-1.0797</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1318</v>
+        <v>0.4884</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2037</v>
+        <v>0.3454</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9281</v>
+        <v>0.143</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.3787</v>
+        <v>1.8279</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>1.4959</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7145</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1528</v>
+        <v>-2.1504</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4884</v>
+        <v>-3.2596</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3356</v>
+        <v>1.1091</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8217</v>
+        <v>0.9492</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7025</v>
+        <v>0.0049</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1192</v>
+        <v>0.9443</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9786</v>
+        <v>0.4346</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9392</v>
+        <v>0.4336</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0395</v>
+        <v>0.001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8431</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7634</v>
+        <v>-0.4287</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0797</v>
+        <v>0.9433</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2317</v>
+        <v>0.1506</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1432</v>
+        <v>-0.3417</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0885</v>
+        <v>0.4923</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8279</v>
+        <v>-1.8828</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4959</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3321</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6742</v>
+        <v>-2.1924</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9467</v>
+        <v>-1.2559</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2725</v>
+        <v>-0.9365</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9492</v>
+        <v>-0.8084</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0049</v>
+        <v>-1.2663</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9443</v>
+        <v>0.458</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4346</v>
+        <v>-0.8629</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4336</v>
+        <v>-1.5912</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001</v>
+        <v>0.7284</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.0545</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4287</v>
+        <v>0.3249</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9433</v>
+        <v>-0.2704</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3732</v>
+        <v>0.8226</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0289</v>
+        <v>0.4664</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.3561</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8828</v>
+        <v>-3.3787</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.58460000000001</v>
+        <v>14.4926</v>
       </c>
       <c r="E13" t="n">
-        <v>7.490699999999999</v>
+        <v>8.398600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>6.093999999999999</v>
+        <v>6.0938</v>
       </c>
       <c r="G13" t="n">
         <v>9.8352</v>
@@ -1468,13 +1468,13 @@
         <v>18.5575</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7925</v>
+        <v>3.700299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8264999999999998</v>
+        <v>1.7343</v>
       </c>
       <c r="U13" t="n">
-        <v>1.966</v>
+        <v>1.9659</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9962999999999997</v>
@@ -1483,7 +1483,7 @@
         <v>6.8152</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.811400000000001</v>
+        <v>-7.8114</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3487</v>
+        <v>1.5043</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5638</v>
+        <v>1.6649</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2151</v>
+        <v>-0.1607</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0453</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0033</v>
+        <v>0.1589</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1127</v>
+        <v>-0.0116</v>
       </c>
       <c r="U14" t="n">
-        <v>0.116</v>
+        <v>0.1705</v>
       </c>
       <c r="V14" t="n">
         <v>1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2512</v>
+        <v>0.6524</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2914</v>
+        <v>-0.4164</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9599</v>
+        <v>1.0688</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9824000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1787</v>
+        <v>0.5799</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9245</v>
+        <v>0.2167</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2542</v>
+        <v>0.3631</v>
       </c>
       <c r="V15" t="n">
         <v>0.6642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0114</v>
+        <v>-0.233</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1883</v>
+        <v>-0.115</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1997</v>
+        <v>-0.118</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3355</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1288</v>
+        <v>-0.0929</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1899</v>
+        <v>-0.1134</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0612</v>
+        <v>0.0206</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4166</v>
+        <v>-0.2352</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7806</v>
+        <v>0.8817</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1972</v>
+        <v>-1.1168</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2707</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.892</v>
+        <v>-0.7105</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4078</v>
+        <v>-0.3275</v>
       </c>
       <c r="V17" t="n">
         <v>0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8016</v>
+        <v>-1.3034</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.395</v>
+        <v>-0.5972</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4066</v>
+        <v>-0.7062</v>
       </c>
       <c r="G18" t="n">
         <v>-3.2397</v>
@@ -1858,13 +1858,13 @@
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0457</v>
+        <v>-0.5475</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4153</v>
+        <v>-0.6175</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3696</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>3.6559</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6026</v>
+        <v>-1.3861</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7171</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8855</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9661</v>
@@ -1936,13 +1936,13 @@
         <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1096</v>
+        <v>0.3261</v>
       </c>
       <c r="T19" t="n">
         <v>0.0772</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0323</v>
+        <v>0.2489</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9414</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8928</v>
+        <v>-2.6569</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1474</v>
+        <v>-1.0463</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7454</v>
+        <v>-1.6106</v>
       </c>
       <c r="G20" t="n">
         <v>1.029</v>
@@ -2014,13 +2014,13 @@
         <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9767</v>
+        <v>-0.7408</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5364</v>
+        <v>-0.4352</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4404</v>
+        <v>-0.3055</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7731</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9281</v>
+        <v>-3.0293</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2489</v>
+        <v>-2.3501</v>
       </c>
       <c r="F21" t="n">
         <v>-0.6792</v>
@@ -2092,10 +2092,10 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.1011</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0689</v>
+        <v>-0.0322</v>
       </c>
       <c r="U21" t="n">
         <v>-0.0689</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5322</v>
+        <v>-3.0746</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3196</v>
+        <v>-2.9151</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2126</v>
+        <v>-0.1595</v>
       </c>
       <c r="G22" t="n">
         <v>-2.966</v>
@@ -2170,13 +2170,13 @@
         <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7615</v>
+        <v>-0.304</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5969</v>
+        <v>-0.1924</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1647</v>
+        <v>-0.1116</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9992</v>
+        <v>-3.1488</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.09</v>
+        <v>-0.4833</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9093</v>
+        <v>-2.6655</v>
       </c>
       <c r="G23" t="n">
         <v>0.065</v>
@@ -2248,13 +2248,13 @@
         <v>2.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5369</v>
+        <v>-0.6864</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0811</v>
+        <v>-0.4744</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4558</v>
+        <v>-0.212</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5507</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.5846</v>
+        <v>-12.9106</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0939</v>
+        <v>-6.093899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.4907</v>
+        <v>-6.816600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-9.8352</v>
@@ -2326,13 +2326,13 @@
         <v>16.6043</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7924</v>
+        <v>-2.1183</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9661</v>
+        <v>-1.9659</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8267</v>
+        <v>-0.1524</v>
       </c>
       <c r="V24" t="n">
         <v>0.9963000000000006</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484290_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484290_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,47 +549,52 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.952199999999999</v>
+        <v>8.4312</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1942</v>
+        <v>6.6732</v>
       </c>
       <c r="F2" t="n">
         <v>1.758</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9617</v>
+        <v>5.4408</v>
       </c>
       <c r="H2" t="n">
-        <v>3.886</v>
+        <v>3.579</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0758</v>
+        <v>1.8618</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9866</v>
+        <v>5.4657</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5843</v>
+        <v>4.2773</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4023</v>
+        <v>1.1883</v>
       </c>
       <c r="M2" t="n">
         <v>-0.0249</v>
@@ -626,48 +631,53 @@
       </c>
       <c r="X2" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6543</v>
+        <v>2.8334</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1918</v>
+        <v>1.3708</v>
       </c>
       <c r="F3" t="n">
         <v>1.4626</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1027</v>
+        <v>1.2817</v>
       </c>
       <c r="H3" t="n">
         <v>1.8082</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2945</v>
+        <v>-0.5264</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9372</v>
+        <v>2.1163</v>
       </c>
       <c r="K3" t="n">
         <v>1.9672</v>
       </c>
       <c r="L3" t="n">
-        <v>1.97</v>
+        <v>0.149</v>
       </c>
       <c r="M3" t="n">
         <v>-0.8346</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,309 +880,329 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3642</v>
+        <v>1.821</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4775</v>
+        <v>1.821</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1134</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0022</v>
+        <v>1.821</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4707</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.473</v>
+        <v>1.821</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1668</v>
+        <v>1.821</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9644</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2023</v>
+        <v>1.821</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.169</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4937</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.161</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0689</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2299</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0635</v>
+        <v>1.521</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5491</v>
+        <v>1.521</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5144</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7361</v>
+        <v>1.521</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1701</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5659</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8209</v>
+        <v>1.521</v>
       </c>
       <c r="K7" t="n">
-        <v>1.659</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0848</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4889</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0419</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.295</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1792</v>
+        <v>1.3642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6619</v>
+        <v>1.4775</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4827</v>
+        <v>-0.1134</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0581</v>
+        <v>-0.0022</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2336</v>
+        <v>0.4707</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1755</v>
+        <v>-0.473</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6213</v>
+        <v>1.1668</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>0.9644</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5803</v>
+        <v>0.2023</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6793</v>
+        <v>-1.169</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2745</v>
+        <v>-0.4937</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4049</v>
+        <v>-0.6753</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0419</v>
+        <v>-0.161</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0406</v>
+        <v>0.0689</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0014</v>
+        <v>-0.2299</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1863</v>
+        <v>1.221</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0897</v>
+        <v>1.221</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5212</v>
+        <v>1.221</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7368</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2156</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1628</v>
+        <v>1.221</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0819</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8186</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0791</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0805</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0014</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,558 +1212,594 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8961</v>
+        <v>1.0635</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2862</v>
+        <v>0.5491</v>
       </c>
       <c r="F10" t="n">
-        <v>0.39</v>
+        <v>0.5144</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8217</v>
+        <v>1.7361</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7025</v>
+        <v>1.1701</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1192</v>
+        <v>0.5659</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9786</v>
+        <v>1.8209</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9392</v>
+        <v>1.659</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0395</v>
+        <v>0.1619</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8431</v>
+        <v>-0.0848</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7634</v>
+        <v>-0.4889</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0797</v>
+        <v>0.4041</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4884</v>
+        <v>0.0419</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3454</v>
+        <v>-0.295</v>
       </c>
       <c r="U10" t="n">
-        <v>0.143</v>
+        <v>0.3369</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8279</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1504</v>
+        <v>0.1792</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2596</v>
+        <v>0.6619</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1091</v>
+        <v>-0.4827</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9492</v>
+        <v>-0.0581</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0049</v>
+        <v>-0.2336</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9443</v>
+        <v>0.1755</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4346</v>
+        <v>0.6213</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4336</v>
+        <v>0.0409</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001</v>
+        <v>0.5803</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5145999999999999</v>
+        <v>-0.6793</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4287</v>
+        <v>-0.2745</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9433</v>
+        <v>-0.4049</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1506</v>
+        <v>0.0419</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3417</v>
+        <v>0.0406</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4923</v>
+        <v>0.0014</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1924</v>
+        <v>-1.1863</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2559</v>
+        <v>-1.0897</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9365</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8084</v>
+        <v>-0.5212</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2663</v>
+        <v>-0.7368</v>
       </c>
       <c r="I12" t="n">
-        <v>0.458</v>
+        <v>0.2156</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8629</v>
+        <v>0.1628</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5912</v>
+        <v>0.0819</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7284</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0545</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3249</v>
+        <v>-0.8186</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2704</v>
+        <v>0.1346</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8226</v>
+        <v>-0.0791</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4664</v>
+        <v>-0.0805</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3561</v>
+        <v>0.0014</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.3787</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.4926</v>
+        <v>-2.1504</v>
       </c>
       <c r="E13" t="n">
-        <v>8.398600000000002</v>
+        <v>-3.2596</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0938</v>
+        <v>1.1091</v>
       </c>
       <c r="G13" t="n">
-        <v>9.8352</v>
+        <v>0.9492</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7683</v>
+        <v>0.0049</v>
       </c>
       <c r="I13" t="n">
-        <v>6.0669</v>
+        <v>0.9443</v>
       </c>
       <c r="J13" t="n">
-        <v>16.4534</v>
+        <v>0.4346</v>
       </c>
       <c r="K13" t="n">
-        <v>9.030200000000001</v>
+        <v>0.4336</v>
       </c>
       <c r="L13" t="n">
-        <v>7.423</v>
+        <v>0.001</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.618200000000001</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.262099999999999</v>
+        <v>-0.4287</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3561</v>
+        <v>0.9433</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.6043</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>18.5575</v>
+        <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>3.700299999999999</v>
+        <v>0.1506</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7343</v>
+        <v>-0.3417</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9659</v>
+        <v>0.4923</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9962999999999997</v>
+        <v>-1.8828</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8152</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.8114</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5043</v>
+        <v>-2.1924</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6649</v>
+        <v>-1.2559</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1607</v>
+        <v>-0.9365</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0453</v>
+        <v>-0.8084</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3576</v>
+        <v>-1.2663</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6877</v>
+        <v>0.458</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4579</v>
+        <v>-0.8629</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4707</v>
+        <v>-1.5912</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0128</v>
+        <v>0.7284</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5032</v>
+        <v>0.0545</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8283</v>
+        <v>0.3249</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.2704</v>
       </c>
       <c r="P14" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1589</v>
+        <v>0.8226</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0116</v>
+        <v>0.4664</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1705</v>
+        <v>0.3561</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>-3.3787</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6524</v>
+        <v>-3.1171</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4164</v>
+        <v>-3.5071</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0688</v>
+        <v>0.39</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-5.0427</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3868</v>
+        <v>-3.3165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4045</v>
+        <v>-1.7262</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6332</v>
+        <v>-3.1996</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6332</v>
+        <v>-2.5531</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6465</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3492</v>
+        <v>-1.8431</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7536</v>
+        <v>-0.7634</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4045</v>
+        <v>-1.0797</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5799</v>
+        <v>0.4884</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2167</v>
+        <v>0.3454</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3631</v>
+        <v>0.143</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.233</v>
+        <v>14.4927</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.115</v>
+        <v>8.3987</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.118</v>
+        <v>6.0938</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3355</v>
+        <v>9.8353</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3756</v>
+        <v>3.768299999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0401</v>
+        <v>6.067</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6979</v>
+        <v>16.45360000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6574</v>
+        <v>9.0303</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>7.423</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0334</v>
+        <v>-6.6182</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.033</v>
+        <v>-5.262099999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0004</v>
+        <v>-1.3561</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-16.6043</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>18.5575</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0929</v>
+        <v>3.700299999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1134</v>
+        <v>1.7343</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0206</v>
+        <v>1.9659</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9962999999999993</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>6.8152</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-7.8114</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2352</v>
+        <v>1.5043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8817</v>
+        <v>1.6649</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1168</v>
+        <v>-0.1607</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2707</v>
+        <v>-1.0453</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4983</v>
+        <v>-0.3576</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.769</v>
+        <v>-0.6877</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0228</v>
+        <v>0.4579</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.4707</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>-0.0128</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2935</v>
+        <v>-1.5032</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.484</v>
+        <v>-0.8283</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8095</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7105</v>
+        <v>0.1589</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3831</v>
+        <v>-0.0116</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3275</v>
+        <v>0.1705</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
         <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VICENS MOREY</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3034</v>
+        <v>0.6524</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5972</v>
+        <v>-0.4164</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7062</v>
+        <v>1.0688</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2397</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3651</v>
+        <v>-1.3868</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8746</v>
+        <v>0.4045</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9827</v>
+        <v>-0.6332</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3224</v>
+        <v>-0.6332</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6603</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2571</v>
+        <v>-0.3492</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0427</v>
+        <v>-0.7536</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2144</v>
+        <v>0.4045</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5475</v>
+        <v>0.5799</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6175</v>
+        <v>0.2167</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3631</v>
       </c>
       <c r="V18" t="n">
-        <v>3.6559</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9331</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3861</v>
+        <v>-0.233</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7171</v>
+        <v>-0.115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.118</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9661</v>
+        <v>-0.3355</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9875</v>
+        <v>-0.3756</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.9536</v>
+        <v>0.0401</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8818</v>
+        <v>0.6979</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6209</v>
+        <v>0.6574</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.739</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.848</v>
+        <v>-1.0334</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6334</v>
+        <v>-1.033</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>-0.0004</v>
       </c>
       <c r="P19" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3261</v>
+        <v>-0.0929</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0772</v>
+        <v>-0.1134</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2489</v>
+        <v>0.0206</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6569</v>
+        <v>-0.2352</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0463</v>
+        <v>0.8817</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6106</v>
+        <v>-1.1168</v>
       </c>
       <c r="G20" t="n">
-        <v>1.029</v>
+        <v>-0.2707</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6032</v>
+        <v>0.4983</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6322</v>
+        <v>-0.769</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2958</v>
+        <v>1.0228</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7188</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>2.577</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2668</v>
+        <v>-1.2935</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3221</v>
+        <v>-0.484</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9447</v>
+        <v>-0.8095</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7408</v>
+        <v>-0.7105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4352</v>
+        <v>-0.3831</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3055</v>
+        <v>-0.3275</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7731</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7731</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. VICENS MOREY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0293</v>
+        <v>-1.3034</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3501</v>
+        <v>-0.5972</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6792</v>
+        <v>-0.7062</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1235</v>
+        <v>-3.2397</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2648</v>
+        <v>-1.3651</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3883</v>
+        <v>-1.8746</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3644</v>
+        <v>-0.9827</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3492</v>
+        <v>-0.3224</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7136</v>
+        <v>-0.6603</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7591</v>
+        <v>-2.2571</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0844</v>
+        <v>-1.0427</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6747</v>
+        <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1011</v>
+        <v>-0.5475</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0322</v>
+        <v>-0.6175</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0689</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.9331</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2226,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0746</v>
+        <v>-1.3861</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9151</v>
+        <v>-0.7171</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1595</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.966</v>
+        <v>-0.9661</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1717</v>
+        <v>1.9875</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7943</v>
+        <v>-2.9536</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7692</v>
+        <v>0.8818</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6498</v>
+        <v>2.6209</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1194</v>
+        <v>-1.739</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1967</v>
+        <v>-1.848</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5219</v>
+        <v>-0.6334</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-1.2146</v>
       </c>
       <c r="P22" t="n">
         <v>0.1953</v>
@@ -2170,28 +2271,33 @@
         <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.304</v>
+        <v>0.3261</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1924</v>
+        <v>0.0772</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1116</v>
+        <v>0.2489</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1488</v>
+        <v>-2.6569</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4833</v>
+        <v>-1.0463</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6655</v>
+        <v>-1.6106</v>
       </c>
       <c r="G23" t="n">
-        <v>0.065</v>
+        <v>1.029</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2589</v>
+        <v>-0.6032</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3239</v>
+        <v>1.6322</v>
       </c>
       <c r="J23" t="n">
-        <v>3.0114</v>
+        <v>3.2958</v>
       </c>
       <c r="K23" t="n">
-        <v>1.068</v>
+        <v>0.7188</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9433</v>
+        <v>2.577</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9463</v>
+        <v>-2.2668</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3269</v>
+        <v>-1.3221</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6194</v>
+        <v>-0.9447</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q23" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9301</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6864</v>
+        <v>-0.7408</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4744</v>
+        <v>-0.4352</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.212</v>
+        <v>-0.3055</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5507</v>
+        <v>-1.7731</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.0293</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.3501</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.6792</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.1235</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.3883</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.7136</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.7591</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1011</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.0689</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I. MARTINEZ MESEGUER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.0746</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.9151</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.1595</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.966</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.1717</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.7943</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.7692</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6498</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.1194</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.1967</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.5219</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.304</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1924</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1116</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E. ZUSTOVICH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.1488</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.4833</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.6655</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2589</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.0114</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.9433</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.9463</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.3269</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.6194</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.6864</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.4744</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.212</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.5507</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484290_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-12.9106</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>-6.093899999999999</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>-6.816600000000001</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-9.8352</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>-3.7683</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>-6.0668</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J27" t="n">
         <v>6.6181</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>5.262</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>1.3562</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>-16.4533</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-9.0303</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>-7.423</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-1.9535</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-18.5575</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>16.6043</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>-2.1183</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>-1.9659</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>-0.1524</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>0.9963000000000006</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>7.811199999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-6.815</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
